--- a/results/bar_graph_table.xlsx
+++ b/results/bar_graph_table.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ardal\Desktop\notebooks for GitHub\ai-compound-target-extractor\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61507C27-1DD2-4C8D-9F41-AF6F184AB3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F7AFA8-1000-4E3C-8D51-78429E1C0F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-107" yWindow="-107" windowWidth="20847" windowHeight="12401" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AA$20</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
@@ -589,12 +592,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -624,11 +633,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1082,7 +1092,7 @@
       <c r="K2" t="s">
         <v>76</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="M2" t="s">
@@ -1094,7 +1104,7 @@
       <c r="O2" t="s">
         <v>108</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="2" t="s">
         <v>111</v>
       </c>
       <c r="Q2" t="s">
@@ -1115,7 +1125,7 @@
       <c r="V2" t="s">
         <v>146</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" s="2" t="s">
         <v>150</v>
       </c>
       <c r="X2" t="s">
@@ -1177,7 +1187,7 @@
       <c r="R3" t="s">
         <v>121</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S3" s="2" t="s">
         <v>122</v>
       </c>
       <c r="U3" t="s">
@@ -1233,7 +1243,7 @@
       <c r="N4" t="s">
         <v>99</v>
       </c>
-      <c r="O4" t="s">
+      <c r="O4" s="2" t="s">
         <v>110</v>
       </c>
       <c r="P4" t="s">
@@ -1280,7 +1290,7 @@
       <c r="I5" t="s">
         <v>68</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="2" t="s">
         <v>73</v>
       </c>
       <c r="K5" t="s">
@@ -1488,7 +1498,7 @@
       <c r="N10" t="s">
         <v>105</v>
       </c>
-      <c r="P10" t="s">
+      <c r="P10" s="2" t="s">
         <v>113</v>
       </c>
       <c r="S10" t="s">
@@ -1520,13 +1530,13 @@
       <c r="S11" t="s">
         <v>127</v>
       </c>
-      <c r="U11" t="s">
+      <c r="U11" s="2" t="s">
         <v>144</v>
       </c>
       <c r="X11" t="s">
         <v>164</v>
       </c>
-      <c r="AA11" t="s">
+      <c r="AA11" s="2" t="s">
         <v>110</v>
       </c>
     </row>
@@ -1546,13 +1556,13 @@
       <c r="S12" t="s">
         <v>128</v>
       </c>
-      <c r="U12" t="s">
+      <c r="U12" s="2" t="s">
         <v>145</v>
       </c>
       <c r="X12" t="s">
         <v>165</v>
       </c>
-      <c r="AA12" t="s">
+      <c r="AA12" s="2" t="s">
         <v>181</v>
       </c>
     </row>
@@ -1593,7 +1603,7 @@
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="2" t="s">
         <v>41</v>
       </c>
       <c r="S16" t="s">
@@ -1606,12 +1616,12 @@
       </c>
     </row>
     <row r="18" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S18" t="s">
+      <c r="S18" s="2" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="19" spans="19:19" x14ac:dyDescent="0.3">
-      <c r="S19" t="s">
+      <c r="S19" s="2" t="s">
         <v>134</v>
       </c>
     </row>
@@ -1621,6 +1631,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AA20" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>